--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128514698</v>
+        <v>128514342</v>
       </c>
       <c r="B2" t="n">
-        <v>82942</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389513</v>
+        <v>390058</v>
       </c>
       <c r="R2" t="n">
-        <v>7025758</v>
+        <v>7026339</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128514342</v>
+        <v>128514698</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>82942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>390058</v>
+        <v>389513</v>
       </c>
       <c r="R3" t="n">
-        <v>7026339</v>
+        <v>7025758</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514783</v>
+        <v>128514494</v>
       </c>
       <c r="B7" t="n">
-        <v>91470</v>
+        <v>82942</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389409</v>
+        <v>389911</v>
       </c>
       <c r="R7" t="n">
-        <v>7025978</v>
+        <v>7026113</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514494</v>
+        <v>128514783</v>
       </c>
       <c r="B8" t="n">
-        <v>82942</v>
+        <v>91470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389911</v>
+        <v>389409</v>
       </c>
       <c r="R8" t="n">
-        <v>7026113</v>
+        <v>7025978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128514342</v>
+        <v>128514698</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>82942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>390058</v>
+        <v>389513</v>
       </c>
       <c r="R2" t="n">
-        <v>7026339</v>
+        <v>7025758</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128514698</v>
+        <v>128514342</v>
       </c>
       <c r="B3" t="n">
-        <v>82942</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389513</v>
+        <v>390058</v>
       </c>
       <c r="R3" t="n">
-        <v>7025758</v>
+        <v>7026339</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514494</v>
+        <v>128514783</v>
       </c>
       <c r="B7" t="n">
-        <v>82942</v>
+        <v>91470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389911</v>
+        <v>389409</v>
       </c>
       <c r="R7" t="n">
-        <v>7026113</v>
+        <v>7025978</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514783</v>
+        <v>128514494</v>
       </c>
       <c r="B8" t="n">
-        <v>91470</v>
+        <v>82942</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389409</v>
+        <v>389911</v>
       </c>
       <c r="R8" t="n">
-        <v>7025978</v>
+        <v>7026113</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128514698</v>
       </c>
       <c r="B2" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128514342</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128514655</v>
       </c>
       <c r="B4" t="n">
-        <v>78443</v>
+        <v>78447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128514428</v>
       </c>
       <c r="B5" t="n">
-        <v>78060</v>
+        <v>78064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128514426</v>
       </c>
       <c r="B6" t="n">
-        <v>75171</v>
+        <v>75175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128514783</v>
       </c>
       <c r="B7" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128514494</v>
       </c>
       <c r="B8" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128514455</v>
       </c>
       <c r="B9" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128514489</v>
       </c>
       <c r="B10" t="n">
-        <v>79339</v>
+        <v>79343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128514761</v>
       </c>
       <c r="B11" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128514763</v>
       </c>
       <c r="B12" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514783</v>
+        <v>128514494</v>
       </c>
       <c r="B7" t="n">
-        <v>91476</v>
+        <v>82946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389409</v>
+        <v>389911</v>
       </c>
       <c r="R7" t="n">
-        <v>7025978</v>
+        <v>7026113</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514494</v>
+        <v>128514783</v>
       </c>
       <c r="B8" t="n">
-        <v>82946</v>
+        <v>91482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389911</v>
+        <v>389409</v>
       </c>
       <c r="R8" t="n">
-        <v>7026113</v>
+        <v>7025978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>128514455</v>
       </c>
       <c r="B9" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128514761</v>
       </c>
       <c r="B11" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128514763</v>
       </c>
       <c r="B12" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128514698</v>
       </c>
       <c r="B2" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128514342</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128514655</v>
       </c>
       <c r="B4" t="n">
-        <v>78447</v>
+        <v>78449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128514428</v>
       </c>
       <c r="B5" t="n">
-        <v>78064</v>
+        <v>78066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128514426</v>
       </c>
       <c r="B6" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514494</v>
+        <v>128514783</v>
       </c>
       <c r="B7" t="n">
-        <v>82946</v>
+        <v>91484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389911</v>
+        <v>389409</v>
       </c>
       <c r="R7" t="n">
-        <v>7026113</v>
+        <v>7025978</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514783</v>
+        <v>128514494</v>
       </c>
       <c r="B8" t="n">
-        <v>91482</v>
+        <v>82948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389409</v>
+        <v>389911</v>
       </c>
       <c r="R8" t="n">
-        <v>7025978</v>
+        <v>7026113</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>128514455</v>
       </c>
       <c r="B9" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128514489</v>
       </c>
       <c r="B10" t="n">
-        <v>79343</v>
+        <v>79345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128514761</v>
       </c>
       <c r="B11" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128514763</v>
       </c>
       <c r="B12" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514783</v>
+        <v>128514494</v>
       </c>
       <c r="B7" t="n">
-        <v>91484</v>
+        <v>82948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389409</v>
+        <v>389911</v>
       </c>
       <c r="R7" t="n">
-        <v>7025978</v>
+        <v>7026113</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514494</v>
+        <v>128514783</v>
       </c>
       <c r="B8" t="n">
-        <v>82948</v>
+        <v>91484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389911</v>
+        <v>389409</v>
       </c>
       <c r="R8" t="n">
-        <v>7026113</v>
+        <v>7025978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>128514783</v>
       </c>
       <c r="B8" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128514455</v>
       </c>
       <c r="B9" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128514761</v>
       </c>
       <c r="B11" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128514763</v>
       </c>
       <c r="B12" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128514698</v>
       </c>
       <c r="B2" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128514342</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128514655</v>
       </c>
       <c r="B4" t="n">
-        <v>78449</v>
+        <v>78476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128514428</v>
       </c>
       <c r="B5" t="n">
-        <v>78066</v>
+        <v>78093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128514426</v>
       </c>
       <c r="B6" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>128514494</v>
       </c>
       <c r="B7" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>128514783</v>
       </c>
       <c r="B8" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>128514455</v>
       </c>
       <c r="B9" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128514489</v>
       </c>
       <c r="B10" t="n">
-        <v>79345</v>
+        <v>79372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128514761</v>
       </c>
       <c r="B11" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128514763</v>
       </c>
       <c r="B12" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128514698</v>
       </c>
       <c r="B2" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128514342</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128514655</v>
       </c>
       <c r="B4" t="n">
-        <v>78476</v>
+        <v>78480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128514428</v>
       </c>
       <c r="B5" t="n">
-        <v>78093</v>
+        <v>78097</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128514426</v>
       </c>
       <c r="B6" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514494</v>
+        <v>128514783</v>
       </c>
       <c r="B7" t="n">
-        <v>82975</v>
+        <v>91517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389911</v>
+        <v>389409</v>
       </c>
       <c r="R7" t="n">
-        <v>7026113</v>
+        <v>7025978</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514783</v>
+        <v>128514494</v>
       </c>
       <c r="B8" t="n">
-        <v>91512</v>
+        <v>82979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389409</v>
+        <v>389911</v>
       </c>
       <c r="R8" t="n">
-        <v>7025978</v>
+        <v>7026113</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>128514455</v>
       </c>
       <c r="B9" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128514489</v>
       </c>
       <c r="B10" t="n">
-        <v>79372</v>
+        <v>79376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128514761</v>
       </c>
       <c r="B11" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128514763</v>
       </c>
       <c r="B12" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514783</v>
+        <v>128514494</v>
       </c>
       <c r="B7" t="n">
-        <v>91517</v>
+        <v>82979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389409</v>
+        <v>389911</v>
       </c>
       <c r="R7" t="n">
-        <v>7025978</v>
+        <v>7026113</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514494</v>
+        <v>128514783</v>
       </c>
       <c r="B8" t="n">
-        <v>82979</v>
+        <v>91522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389911</v>
+        <v>389409</v>
       </c>
       <c r="R8" t="n">
-        <v>7026113</v>
+        <v>7025978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>128514455</v>
       </c>
       <c r="B9" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128514761</v>
       </c>
       <c r="B11" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128514763</v>
       </c>
       <c r="B12" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128514698</v>
       </c>
       <c r="B2" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128514342</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128514655</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>78484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128514428</v>
       </c>
       <c r="B5" t="n">
-        <v>78097</v>
+        <v>78101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128514426</v>
       </c>
       <c r="B6" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514494</v>
+        <v>128514783</v>
       </c>
       <c r="B7" t="n">
-        <v>82979</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389911</v>
+        <v>389409</v>
       </c>
       <c r="R7" t="n">
-        <v>7026113</v>
+        <v>7025978</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514783</v>
+        <v>128514494</v>
       </c>
       <c r="B8" t="n">
-        <v>91522</v>
+        <v>82983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389409</v>
+        <v>389911</v>
       </c>
       <c r="R8" t="n">
-        <v>7025978</v>
+        <v>7026113</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>128514455</v>
       </c>
       <c r="B9" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128514489</v>
       </c>
       <c r="B10" t="n">
-        <v>79376</v>
+        <v>79380</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128514761</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128514763</v>
       </c>
       <c r="B12" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514783</v>
+        <v>128514494</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>82983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389409</v>
+        <v>389911</v>
       </c>
       <c r="R7" t="n">
-        <v>7025978</v>
+        <v>7026113</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514494</v>
+        <v>128514783</v>
       </c>
       <c r="B8" t="n">
-        <v>82983</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389911</v>
+        <v>389409</v>
       </c>
       <c r="R8" t="n">
-        <v>7026113</v>
+        <v>7025978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128514698</v>
+        <v>128514342</v>
       </c>
       <c r="B2" t="n">
-        <v>82983</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389513</v>
+        <v>390058</v>
       </c>
       <c r="R2" t="n">
-        <v>7025758</v>
+        <v>7026339</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128514342</v>
+        <v>128514698</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>82892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>390058</v>
+        <v>389513</v>
       </c>
       <c r="R3" t="n">
-        <v>7026339</v>
+        <v>7025758</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>128514655</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>78389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128514428</v>
       </c>
       <c r="B5" t="n">
-        <v>78101</v>
+        <v>78042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128514426</v>
       </c>
       <c r="B6" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514494</v>
+        <v>128514783</v>
       </c>
       <c r="B7" t="n">
-        <v>82983</v>
+        <v>91531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389911</v>
+        <v>389409</v>
       </c>
       <c r="R7" t="n">
-        <v>7026113</v>
+        <v>7025978</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514783</v>
+        <v>128514494</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>82892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389409</v>
+        <v>389911</v>
       </c>
       <c r="R8" t="n">
-        <v>7025978</v>
+        <v>7026113</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>128514455</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128514489</v>
       </c>
       <c r="B10" t="n">
-        <v>79380</v>
+        <v>79285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128514761</v>
       </c>
       <c r="B11" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128514763</v>
       </c>
       <c r="B12" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128514698</v>
       </c>
       <c r="B2" t="n">
-        <v>82892</v>
+        <v>82897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128514342</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128514655</v>
       </c>
       <c r="B4" t="n">
-        <v>78389</v>
+        <v>78394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>128514428</v>
       </c>
       <c r="B5" t="n">
-        <v>78042</v>
+        <v>78047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>128514426</v>
       </c>
       <c r="B6" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514783</v>
+        <v>128514494</v>
       </c>
       <c r="B7" t="n">
-        <v>91533</v>
+        <v>82897</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389409</v>
+        <v>389911</v>
       </c>
       <c r="R7" t="n">
-        <v>7025978</v>
+        <v>7026113</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514494</v>
+        <v>128514783</v>
       </c>
       <c r="B8" t="n">
-        <v>82892</v>
+        <v>91538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389911</v>
+        <v>389409</v>
       </c>
       <c r="R8" t="n">
-        <v>7026113</v>
+        <v>7025978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>128514455</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>128514489</v>
       </c>
       <c r="B10" t="n">
-        <v>79285</v>
+        <v>79290</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>128514761</v>
       </c>
       <c r="B11" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>128514763</v>
       </c>
       <c r="B12" t="n">
-        <v>92213</v>
+        <v>92218</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128514698</v>
+        <v>128514655</v>
       </c>
       <c r="B2" t="n">
-        <v>82897</v>
+        <v>78686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>389513</v>
+        <v>389601</v>
       </c>
       <c r="R2" t="n">
-        <v>7025758</v>
+        <v>7025778</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128514342</v>
+        <v>128514761</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>390058</v>
+        <v>389389</v>
       </c>
       <c r="R3" t="n">
-        <v>7026339</v>
+        <v>7025883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,45 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128514655</v>
+        <v>128514494</v>
       </c>
       <c r="B4" t="n">
-        <v>78394</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389601</v>
+        <v>389911</v>
       </c>
       <c r="R4" t="n">
-        <v>7025778</v>
+        <v>7026113</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128514428</v>
+        <v>128514698</v>
       </c>
       <c r="B5" t="n">
-        <v>78047</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>389926</v>
+        <v>389513</v>
       </c>
       <c r="R5" t="n">
-        <v>7026229</v>
+        <v>7025758</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,45 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128514426</v>
+        <v>128514763</v>
       </c>
       <c r="B6" t="n">
-        <v>83010</v>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stordolpen, Stordolpen, Jmt</t>
+          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>389926</v>
+        <v>389378</v>
       </c>
       <c r="R6" t="n">
-        <v>7026229</v>
+        <v>7025903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,32 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128514494</v>
+        <v>128514342</v>
       </c>
       <c r="B7" t="n">
-        <v>82897</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>389911</v>
+        <v>390058</v>
       </c>
       <c r="R7" t="n">
-        <v>7026113</v>
+        <v>7026339</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128514783</v>
+        <v>128514426</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
+          <t>Stordolpen, Stordolpen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>389409</v>
+        <v>389926</v>
       </c>
       <c r="R8" t="n">
-        <v>7025978</v>
+        <v>7026229</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,32 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128514455</v>
+        <v>128514489</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>79583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6459</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>389905</v>
+        <v>389911</v>
       </c>
       <c r="R9" t="n">
-        <v>7026207</v>
+        <v>7026113</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,32 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128514489</v>
+        <v>128514428</v>
       </c>
       <c r="B10" t="n">
-        <v>79290</v>
+        <v>78339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6459</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>389911</v>
+        <v>389926</v>
       </c>
       <c r="R10" t="n">
-        <v>7026113</v>
+        <v>7026229</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,210 +1590,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>128514761</v>
-      </c>
-      <c r="B11" t="n">
-        <v>91520</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>389389</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7025883</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Luckig och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>128514763</v>
-      </c>
-      <c r="B12" t="n">
-        <v>92218</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Sundsbäcken, Sundsbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>389378</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7025903</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Luckig och lövrik grannaturskog i skog-myrmosaik</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1529-2025 artfynd.xlsx
+++ b/artfynd/A 1529-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514655</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514761</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514494</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514698</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514763</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514342</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514426</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514489</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,8 +1635,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128514428</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>